--- a/GUA/Modelos/Energía&Transporte/NuevosEscenarios/Escenario_alto/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
+++ b/GUA/Modelos/Energía&Transporte/NuevosEscenarios/Escenario_alto/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Dropbox\2_WORK\EperLab\Proyectos\2021_PND_GUA\4_Model\OSeMOSYS_GUA\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Desktop\CLG_repositories\openmodels_lac\GUA\Modelos\Energía&amp;Transporte\NuevosEscenarios\Escenario_alto\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEA4B35-7A75-46DF-9244-5221D1E50B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158213B8-B97A-4914-8CAC-10AC5BED4A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3270" windowWidth="26970" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Other_Params" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>BAU</t>
   </si>
   <si>
     <t>Other_Scenarios</t>
-  </si>
-  <si>
-    <t>NDP</t>
   </si>
   <si>
     <t>Region</t>
@@ -236,10 +233,10 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -536,59 +533,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.84375" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -598,6 +593,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a085176836abd262a7ea2e14f8197063">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18610519e5d66159880ace7e9acb3815" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
@@ -820,33 +834,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0F1FB8-67B0-427F-99AE-A2D9A9B067D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B54057-1D5F-44F9-9704-492777A1CA32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B39036F-3C1D-4220-9F39-4BB759B645EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B39036F-3C1D-4220-9F39-4BB759B645EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B54057-1D5F-44F9-9704-492777A1CA32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0F1FB8-67B0-427F-99AE-A2D9A9B067D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>